--- a/backend/reports/users_report.xlsx
+++ b/backend/reports/users_report.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="176">
   <si>
     <t>#</t>
   </si>
@@ -69,7 +69,7 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>₹14331.00</t>
+    <t>₹16447.00</t>
   </si>
   <si>
     <t>Active</t>
@@ -285,6 +285,54 @@
     <t>10/3/2026, 9:14:28 pm</t>
   </si>
   <si>
+    <t>Test User 100</t>
+  </si>
+  <si>
+    <t>test_user_100@buyer.com</t>
+  </si>
+  <si>
+    <t>9450300000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tonk Road, Jaipur Municipal Corporation, Sanganer Tehsil, Jaipur, Rajasthan, 302018, India,  - </t>
+  </si>
+  <si>
+    <t>13/3/2026, 1:57:41 pm</t>
+  </si>
+  <si>
+    <t>13/3/2026, 1:57:48 pm</t>
+  </si>
+  <si>
+    <t>Ravi Drolia</t>
+  </si>
+  <si>
+    <t>ravi@gmail.com</t>
+  </si>
+  <si>
+    <t>9352526219</t>
+  </si>
+  <si>
+    <t>14/3/2026, 1:03:51 am</t>
+  </si>
+  <si>
+    <t>14/3/2026, 1:04:13 am</t>
+  </si>
+  <si>
+    <t>Krrish</t>
+  </si>
+  <si>
+    <t>krish56b1@gmail.com</t>
+  </si>
+  <si>
+    <t>8946912668</t>
+  </si>
+  <si>
+    <t>31/3/2026, 9:46:58 pm</t>
+  </si>
+  <si>
+    <t>31/3/2026, 9:47:25 pm</t>
+  </si>
+  <si>
     <t>Shop Name</t>
   </si>
   <si>
@@ -432,6 +480,42 @@
     <t>8/3/2026, 2:27:49 am</t>
   </si>
   <si>
+    <t>Test Seller 100</t>
+  </si>
+  <si>
+    <t>test_seller_100@shop.com</t>
+  </si>
+  <si>
+    <t>Test Shop in Jaipur</t>
+  </si>
+  <si>
+    <t>J Block - tagore nagar, Nirman Nagar, Jaipur, Jaipur Municipal Corporation, Jaipur Tehsil, Jaipur, Rajasthan, 302001, India, Jaipur, Rajasthan - 302001</t>
+  </si>
+  <si>
+    <t>13/3/2026, 1:59:34 pm</t>
+  </si>
+  <si>
+    <t>13/3/2026, 1:59:39 pm</t>
+  </si>
+  <si>
+    <t>Nigga</t>
+  </si>
+  <si>
+    <t>yobitch@nigga.com</t>
+  </si>
+  <si>
+    <t>6969696969</t>
+  </si>
+  <si>
+    <t>my nigga store</t>
+  </si>
+  <si>
+    <t>Mirza Ismail Road, Jaipur, Jaipur Municipal Corporation, Jaipur Tehsil, Jaipur, Rajasthan, 302001, India, Jaipur, Rajasthan - 302001</t>
+  </si>
+  <si>
+    <t>10/4/2026, 9:27:06 pm</t>
+  </si>
+  <si>
     <t>Metric</t>
   </si>
   <si>
@@ -456,7 +540,7 @@
     <t>Report Generated At</t>
   </si>
   <si>
-    <t>13/3/2026, 1:45:00 pm</t>
+    <t>29/7/2026, 12:07:02 am</t>
   </si>
 </sst>
 </file>
@@ -868,7 +952,7 @@
   <sheetPr>
     <tabColor rgb="FF4CAF50"/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -944,7 +1028,7 @@
         <v>17</v>
       </c>
       <c r="H2" s="2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>18</v>
@@ -1413,6 +1497,120 @@
       </c>
       <c r="L14" s="2" t="s">
         <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15" t="s">
+        <v>19</v>
+      </c>
+      <c r="K15" t="s">
+        <v>94</v>
+      </c>
+      <c r="L15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17" t="s">
+        <v>28</v>
+      </c>
+      <c r="J17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" t="s">
+        <v>104</v>
+      </c>
+      <c r="L17" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1426,7 +1624,7 @@
   <sheetPr>
     <tabColor rgb="FF2196F3"/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1459,28 +1657,28 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
@@ -1500,25 +1698,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>17</v>
@@ -1530,7 +1728,7 @@
         <v>4.6</v>
       </c>
       <c r="L2" s="3">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>27</v>
@@ -1539,7 +1737,7 @@
         <v>19</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>47</v>
@@ -1550,25 +1748,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="E3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="F3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="G3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="H3" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -1589,10 +1787,10 @@
         <v>19</v>
       </c>
       <c r="O3" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="P3" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -1600,25 +1798,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>17</v>
@@ -1630,7 +1828,7 @@
         <v>3.7</v>
       </c>
       <c r="L4" s="3">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>27</v>
@@ -1639,10 +1837,10 @@
         <v>19</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -1650,22 +1848,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="E5" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="F5" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="G5" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="H5" t="s">
         <v>52</v>
@@ -1680,7 +1878,7 @@
         <v>4.3</v>
       </c>
       <c r="L5">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="M5" t="s">
         <v>27</v>
@@ -1689,10 +1887,10 @@
         <v>19</v>
       </c>
       <c r="O5" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="P5" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -1700,25 +1898,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>27</v>
@@ -1730,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>27</v>
@@ -1739,10 +1937,10 @@
         <v>19</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -1750,25 +1948,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="C7" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="D7" t="s">
         <v>63</v>
       </c>
       <c r="E7" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="F7" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="G7" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="H7" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="I7" t="s">
         <v>27</v>
@@ -1780,19 +1978,119 @@
         <v>0</v>
       </c>
       <c r="L7">
+        <v>31</v>
+      </c>
+      <c r="M7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N7" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7" t="s">
+        <v>153</v>
+      </c>
+      <c r="P7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="M7" t="s">
-        <v>17</v>
-      </c>
-      <c r="N7" t="s">
-        <v>19</v>
-      </c>
-      <c r="O7" t="s">
-        <v>137</v>
-      </c>
-      <c r="P7" t="s">
-        <v>138</v>
+      <c r="J8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C9" t="s">
+        <v>162</v>
+      </c>
+      <c r="D9" t="s">
+        <v>163</v>
+      </c>
+      <c r="E9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F9" t="s">
+        <v>118</v>
+      </c>
+      <c r="G9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9" t="s">
+        <v>166</v>
+      </c>
+      <c r="P9" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -1815,50 +2113,50 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>140</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="B2">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="B3">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="B5">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>145</v>
+        <v>173</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1866,15 +2164,15 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>146</v>
+        <v>174</v>
       </c>
       <c r="B8" t="s">
-        <v>147</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
